--- a/output/pdf_financials_xlsx/ADON.xlsx
+++ b/output/pdf_financials_xlsx/ADON.xlsx
@@ -1642,7 +1642,7 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.0222</v>
       </c>
     </row>
     <row r="93">
@@ -2672,7 +2672,11 @@
           <t>Reserve (note 9)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
